--- a/SEC_Excel_Downloads_AAPL_10-K/AAPL_10-K_Master_Consolidated_Financials_RemovedEmptyRowsCols_deduplicated_after_merge.xlsx
+++ b/SEC_Excel_Downloads_AAPL_10-K/AAPL_10-K_Master_Consolidated_Financials_RemovedEmptyRowsCols_deduplicated_after_merge.xlsx
@@ -18,11 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0,&quot;K&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0,,&quot;M&quot;"/>
-  </numFmts>
-  <fonts count="4">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,13 +32,21 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -60,8 +65,20 @@
         <bgColor rgb="FFDEEAF6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F8F8"/>
+        <bgColor rgb="FFF8F8F8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -75,47 +92,66 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00666666"/>
+      </left>
+      <right style="medium">
+        <color rgb="00666666"/>
+      </right>
+      <top style="medium">
+        <color rgb="00666666"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00666666"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="39" fontId="4" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="39" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="39" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -483,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -492,8 +528,6 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,21 +561,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Sep. 29, 2018 &gt; Net sales</t>
+          <t>Sep. 26, 2020 &gt; Net sales</t>
         </is>
       </c>
       <c r="B2" s="5" t="n">
@@ -559,45 +583,33 @@
       <c r="F2" s="5" t="n">
         <v>274515</v>
       </c>
-      <c r="G2" s="5" t="n">
-        <v>260174</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>265595</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Sep. 29, 2018 &gt; Cost of sales</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
+          <t>Sep. 26, 2020 &gt; Cost of sales</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>210352</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>214137</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="6" t="n">
         <v>223546</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="6" t="n">
         <v>212981</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="6" t="n">
         <v>169559</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>161782</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>163756</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Sep. 29, 2018 &gt; Gross margin</t>
+          <t>Sep. 26, 2020 &gt; Gross margin</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
@@ -615,12 +627,6 @@
       <c r="F4" s="5" t="n">
         <v>104956</v>
       </c>
-      <c r="G4" s="5" t="n">
-        <v>98392</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>101839</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -628,26 +634,20 @@
           <t>Operating expenses: &gt; Research and development</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>31370</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>29915</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>26251</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>21914</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>18752</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>16217</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>14236</v>
       </c>
     </row>
     <row r="6">
@@ -671,12 +671,6 @@
       <c r="F6" s="5" t="n">
         <v>19916</v>
       </c>
-      <c r="G6" s="5" t="n">
-        <v>18245</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>16705</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -684,26 +678,20 @@
           <t>Operating expenses: &gt; Total operating expenses</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>57467</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>54847</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>51345</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>43887</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <v>38668</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>34462</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>30941</v>
       </c>
     </row>
     <row r="8">
@@ -727,12 +715,6 @@
       <c r="F8" s="5" t="n">
         <v>66288</v>
       </c>
-      <c r="G8" s="5" t="n">
-        <v>63930</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>70898</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -755,12 +737,6 @@
       <c r="F9" s="6" t="n">
         <v>803</v>
       </c>
-      <c r="G9" s="5" t="n">
-        <v>1807</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>2005</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -783,12 +759,6 @@
       <c r="F10" s="5" t="n">
         <v>67091</v>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>65737</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>72903</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -796,26 +766,20 @@
           <t>Operating expenses: &gt; Provision for income taxes</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>29749</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>16741</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="6" t="n">
         <v>19300</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="6" t="n">
         <v>14527</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="6" t="n">
         <v>9680</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>10481</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>13372</v>
       </c>
     </row>
     <row r="12">
@@ -839,12 +803,6 @@
       <c r="F12" s="5" t="n">
         <v>57411</v>
       </c>
-      <c r="G12" s="5" t="n">
-        <v>55256</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>59531</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -867,12 +825,6 @@
       <c r="F13" s="6" t="n">
         <v>3.31</v>
       </c>
-      <c r="G13" s="6" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -880,26 +832,20 @@
           <t>Earnings per share: &gt; Diluted (in dollars per share)</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="5" t="n">
         <v>6.08</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="5" t="n">
         <v>6.13</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="5" t="n">
         <v>6.11</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="5" t="n">
         <v>5.61</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="5" t="n">
         <v>3.28</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>2.98</v>
       </c>
     </row>
     <row r="15">
@@ -908,26 +854,20 @@
           <t>Shares used in computing earnings per share: &gt; Basic (in shares)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="6" t="n">
         <v>15343783</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="6" t="n">
         <v>15744231</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="6" t="n">
         <v>16215963</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="6" t="n">
         <v>16701272</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="6" t="n">
         <v>17352119</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>18471336</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>19821510</v>
       </c>
     </row>
     <row r="16">
@@ -936,26 +876,20 @@
           <t>Shares used in computing earnings per share: &gt; Diluted (in shares)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="5" t="n">
         <v>15408095</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="5" t="n">
         <v>15812547</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="5" t="n">
         <v>16325819</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" s="5" t="n">
         <v>16864919</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="5" t="n">
         <v>17528214</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>18595651</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>20000435</v>
       </c>
     </row>
     <row r="17">
@@ -964,26 +898,20 @@
           <t>Products &gt; Net sales</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>294866</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="6" t="n">
         <v>298085</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="6" t="n">
         <v>316199</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="6" t="n">
         <v>297392</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="6" t="n">
         <v>220747</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>213883</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>225847</v>
       </c>
     </row>
     <row r="18">
@@ -1007,12 +935,6 @@
       <c r="F18" s="5" t="n">
         <v>151286</v>
       </c>
-      <c r="G18" s="5" t="n">
-        <v>144996</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>148164</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1020,26 +942,20 @@
           <t>Services &gt; Net sales</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>96169</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="6" t="n">
         <v>85200</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="6" t="n">
         <v>78129</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="6" t="n">
         <v>68425</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="6" t="n">
         <v>53768</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>46291</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>39748</v>
       </c>
     </row>
     <row r="20">
@@ -1062,12 +978,6 @@
       </c>
       <c r="F20" s="5" t="n">
         <v>18273</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>16786</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>15592</v>
       </c>
     </row>
   </sheetData>
@@ -1081,7 +991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1089,8 +999,6 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1119,16 +1027,6 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -1148,12 +1046,6 @@
       <c r="E2" s="5" t="n">
         <v>34940</v>
       </c>
-      <c r="F2" s="5" t="n">
-        <v>38016</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>48844</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1161,23 +1053,17 @@
           <t>Current assets: &gt; Marketable securities</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <v>35228</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>31590</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="6" t="n">
         <v>24658</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="6" t="n">
         <v>27699</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>52927</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>51713</v>
       </c>
     </row>
     <row r="4">
@@ -1198,12 +1084,6 @@
       <c r="E4" s="5" t="n">
         <v>26278</v>
       </c>
-      <c r="F4" s="5" t="n">
-        <v>16120</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>22926</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1211,23 +1091,17 @@
           <t>Current assets: &gt; Vendor non-trade receivables</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>32833</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>31477</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>32748</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>25228</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>21325</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>22878</v>
       </c>
     </row>
     <row r="6">
@@ -1248,12 +1122,6 @@
       <c r="E6" s="5" t="n">
         <v>6580</v>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>4061</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>4106</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1261,23 +1129,17 @@
           <t>Current assets: &gt; Other current assets</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>14287</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>14695</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>21223</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>14111</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>11264</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>12352</v>
       </c>
     </row>
     <row r="8">
@@ -1298,12 +1160,6 @@
       <c r="E8" s="5" t="n">
         <v>134836</v>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>143713</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>162819</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1311,23 +1167,17 @@
           <t>Non-current assets: &gt; Marketable securities</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>91479</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>100544</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>120805</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="6" t="n">
         <v>127877</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>100887</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>105341</v>
       </c>
     </row>
     <row r="10">
@@ -1348,12 +1198,6 @@
       <c r="E10" s="5" t="n">
         <v>39440</v>
       </c>
-      <c r="F10" s="5" t="n">
-        <v>36766</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>37378</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1361,23 +1205,17 @@
           <t>Non-current assets: &gt; Other non-current assets</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>74834</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>64758</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="6" t="n">
         <v>54428</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="6" t="n">
         <v>48849</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>42522</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>32978</v>
       </c>
     </row>
     <row r="12">
@@ -1398,36 +1236,24 @@
       <c r="E12" s="5" t="n">
         <v>216166</v>
       </c>
-      <c r="F12" s="5" t="n">
-        <v>180175</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>175697</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Non-current assets: &gt; Total assets / Shareholders’ equity: &gt; Total liabilities and shareholders’ equity / Cash Flow Statement &gt; Total liabilities and shareholders’ equity</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="7" t="n">
         <v>364980</v>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="7" t="n">
         <v>352583</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="7" t="n">
         <v>352755</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="7" t="n">
         <v>351002</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>323888</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>338516</v>
       </c>
     </row>
     <row r="14">
@@ -1448,12 +1274,6 @@
       <c r="E14" s="5" t="n">
         <v>54763</v>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>42296</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>46236</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1461,23 +1281,17 @@
           <t>Current liabilities: &gt; Other current liabilities</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>78304</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <v>58829</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="6" t="n">
         <v>60845</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="6" t="n">
         <v>47493</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>42684</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>37720</v>
       </c>
     </row>
     <row r="16">
@@ -1498,12 +1312,6 @@
       <c r="E16" s="5" t="n">
         <v>7612</v>
       </c>
-      <c r="F16" s="5" t="n">
-        <v>6643</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>5522</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1511,23 +1319,17 @@
           <t>Current liabilities: &gt; Commercial paper</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>9967</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="6" t="n">
         <v>5985</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="6" t="n">
         <v>9982</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="6" t="n">
         <v>6000</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>4996</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>5980</v>
       </c>
     </row>
     <row r="18">
@@ -1548,12 +1350,6 @@
       <c r="E18" s="5" t="n">
         <v>9613</v>
       </c>
-      <c r="F18" s="5" t="n">
-        <v>8773</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>10260</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1561,23 +1357,17 @@
           <t>Current liabilities: &gt; Total current liabilities</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>176392</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="6" t="n">
         <v>145308</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="6" t="n">
         <v>153982</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="6" t="n">
         <v>125481</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>105392</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>105718</v>
       </c>
     </row>
     <row r="20">
@@ -1598,12 +1388,6 @@
       <c r="E20" s="5" t="n">
         <v>109106</v>
       </c>
-      <c r="F20" s="5" t="n">
-        <v>98667</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>91807</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1611,23 +1395,17 @@
           <t>Non-current liabilities: &gt; Other non-current liabilities</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="6" t="n">
         <v>45888</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="6" t="n">
         <v>49848</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="6" t="n">
         <v>49142</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="6" t="n">
         <v>53325</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>54490</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>50503</v>
       </c>
     </row>
     <row r="22">
@@ -1648,12 +1426,6 @@
       <c r="E22" s="5" t="n">
         <v>162431</v>
       </c>
-      <c r="F22" s="5" t="n">
-        <v>153157</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>142310</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1661,167 +1433,122 @@
           <t>Non-current liabilities: &gt; Total liabilities</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>308030</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="6" t="n">
         <v>290437</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D23" s="6" t="n">
         <v>302083</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="6" t="n">
         <v>287912</v>
       </c>
-      <c r="F23" s="5" t="n">
-        <v>258549</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>248028</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Commitments and contingencies &gt; Common stock, shares outstanding (in shares) / Shareholders’ equity: &gt; Common stock, shares issued (in shares)</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="7" t="n">
         <v>15116786</v>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="7" t="n">
         <v>15550061</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="7" t="n">
         <v>15943425</v>
       </c>
-      <c r="E24" s="11" t="inlineStr"/>
-      <c r="F24" s="11" t="inlineStr"/>
-      <c r="G24" s="11" t="inlineStr"/>
+      <c r="E24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Shareholders’ equity: &gt; Common stock and additional paid-in capital, $0.00001 par value: 50,400,000 shares authorized; 15,943,425 and 16,426,786 shares issued and outstanding, respectively / Shareholders’ equity: &gt; Common stock and additional paid-in capital, $0.00001 par value: 50,400,000 shares authorized; 16,426,786 and 16,976,763 shares issued and outstanding, respectively / Shareholders’ equity: &gt; Common stock and additional paid-in capital, $0.00001 par value: 50,400,000 shares authorized; 15,550,061 and 15,943,425 shares issued and outstanding, respectively</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr"/>
-      <c r="C25" s="9" t="n">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Shareholders’ equity: &gt; Common stock and additional paid-in capital, $0.00001 par value: 50,400,000 shares authorized; 15,943,425 and 16,426,786 shares issued and outstanding, respectively / Shareholders’ equity: &gt; Common stock and additional paid-in capital, $0.00001 par value: 50,400,000 shares authorized; 15,550,061 and 15,943,425 shares issued and outstanding, respectively</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr"/>
+      <c r="C25" s="7" t="n">
         <v>73812</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="7" t="n">
         <v>64849</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="7" t="n">
         <v>57365</v>
       </c>
-      <c r="F25" s="9" t="n">
-        <v>50779</v>
-      </c>
-      <c r="G25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Shareholders’ equity: &gt; Common stock and additional paid-in capital, $0.00001 par value: 50,400,000 shares authorized; 16,976,763 and 17,772,945 shares issued and outstanding, respectively</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="5" t="n">
-        <v>50779</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>45174</v>
+          <t>Shareholders’ equity: &gt; Retained earnings/(Accumulated deficit) / Shareholders’ equity: &gt; Accumulated deficit</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>-19154</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>-214</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>-3068</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>5562</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Shareholders’ equity: &gt; Retained earnings/(Accumulated deficit) / Shareholders’ equity: &gt; Retained earnings / Shareholders’ equity: &gt; Accumulated deficit</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n">
-        <v>-19154</v>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>-214</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>-3068</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>5562</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>14966</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>45898</v>
-      </c>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Shareholders’ equity: &gt; Common stock and additional paid-in capital, $0.00001 par value: 50,400,000 shares authorized; 15,116,786 and 15,550,061 shares issued and outstanding, respectively</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>83276</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>73812</v>
+      </c>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Shareholders’ equity: &gt; Common stock and additional paid-in capital, $0.00001 par value: 50,400,000 shares authorized; 15,116,786 and 15,550,061 shares issued and outstanding, respectively</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>83276</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>73812</v>
-      </c>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
+          <t>Shareholders’ equity: &gt; Accumulated other comprehensive income/(loss) / Shareholders’ equity: &gt; Accumulated other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>-7172</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>-11452</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>-11109</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>163</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Shareholders’ equity: &gt; Accumulated other comprehensive income/(loss) / Shareholders’ equity: &gt; Accumulated other comprehensive loss</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="n">
-        <v>-7172</v>
-      </c>
-      <c r="C29" s="9" t="n">
-        <v>-11452</v>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>-11109</v>
-      </c>
-      <c r="E29" s="13" t="n">
-        <v>163</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>-406</v>
-      </c>
-      <c r="G29" s="13" t="n">
-        <v>-584</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Shareholders’ equity: &gt; Total shareholders’ equity</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B29" s="6" t="n">
         <v>56950</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C29" s="6" t="n">
         <v>62146</v>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D29" s="6" t="n">
         <v>50672</v>
       </c>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="12" t="n"/>
+      <c r="E29" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1834,7 +1561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1843,8 +1570,6 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1878,43 +1603,27 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Statement of Cash Flows [Abstract] &gt; Cash, cash equivalents, and restricted cash and cash equivalents, beginning balances / Statement of Cash Flows [Abstract] &gt; Cash, cash equivalents and restricted cash, beginning balances</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="7" t="n">
         <v>30737</v>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" s="7" t="n">
         <v>24977</v>
       </c>
-      <c r="D2" s="9" t="n">
+      <c r="D2" s="7" t="n">
         <v>35929</v>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E2" s="7" t="n">
         <v>39789</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" s="7" t="n">
         <v>50224</v>
-      </c>
-      <c r="G2" s="9" t="n">
-        <v>25913</v>
-      </c>
-      <c r="H2" s="9" t="n">
-        <v>20289</v>
       </c>
     </row>
     <row r="3">
@@ -1923,26 +1632,20 @@
           <t>Operating activities: &gt; Net income</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <v>93736</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="6" t="n">
         <v>96995</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="6" t="n">
         <v>99803</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="6" t="n">
         <v>94680</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="6" t="n">
         <v>57411</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>55256</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>59531</v>
       </c>
     </row>
     <row r="4">
@@ -1966,12 +1669,6 @@
       <c r="F4" s="5" t="n">
         <v>11056</v>
       </c>
-      <c r="G4" s="5" t="n">
-        <v>12547</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>10903</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1979,26 +1676,20 @@
           <t>Adjustments to reconcile net income to cash generated by operating activities: &gt; Share-based compensation expense</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>11688</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>10833</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>9038</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>7906</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>6829</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>6068</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>5340</v>
       </c>
     </row>
     <row r="6">
@@ -2019,32 +1710,24 @@
       <c r="E6" s="5" t="n">
         <v>-4921</v>
       </c>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="12" t="n"/>
+      <c r="F6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Adjustments to reconcile net income to cash generated by operating activities: &gt; Deferred income tax expense/(benefit) / Adjustments to reconcile net income to cash generated by operating activities: &gt; Deferred income tax benefit</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr"/>
-      <c r="C7" s="11" t="inlineStr"/>
-      <c r="D7" s="13" t="n">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Adjustments to reconcile net income to cash generated by operating activities: &gt; Deferred income tax expense/(benefit)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="6" t="n">
         <v>895</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="6" t="n">
         <v>-4774</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="6" t="n">
         <v>-215</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>-340</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>-32590</v>
       </c>
     </row>
     <row r="8">
@@ -2053,22 +1736,16 @@
           <t>Changes in operating assets and liabilities: &gt; Other</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="6" t="n">
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="5" t="n">
         <v>-147</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="5" t="n">
         <v>-97</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>-652</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>-444</v>
       </c>
     </row>
     <row r="9">
@@ -2077,26 +1754,20 @@
           <t>Changes in operating assets and liabilities: &gt; Accounts receivable, net</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>-3788</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>-1688</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>-1823</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="6" t="n">
         <v>-10125</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="6" t="n">
         <v>6917</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>245</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>-5322</v>
       </c>
     </row>
     <row r="10">
@@ -2105,8 +1776,8 @@
           <t>Changes in operating assets and liabilities: &gt; Vendor non-trade receivables</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
       <c r="D10" s="5" t="n">
         <v>-7520</v>
       </c>
@@ -2116,12 +1787,6 @@
       <c r="F10" s="5" t="n">
         <v>1553</v>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>2931</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>-8010</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2129,27 +1794,21 @@
           <t>Changes in operating assets and liabilities: &gt; Inventories</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>-1046</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>-1618</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="6" t="n">
         <v>1484</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="6" t="n">
         <v>-2642</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>-127</v>
       </c>
-      <c r="G11" s="6" t="n">
-        <v>-289</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>828</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2172,12 +1831,6 @@
       <c r="F12" s="5" t="n">
         <v>-9588</v>
       </c>
-      <c r="G12" s="6" t="n">
-        <v>873</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>-423</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2185,26 +1838,20 @@
           <t>Changes in operating assets and liabilities: &gt; Accounts payable</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>6020</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>-1889</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="6" t="n">
         <v>9448</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="6" t="n">
         <v>12326</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="6" t="n">
         <v>-4062</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>-1923</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>9175</v>
       </c>
     </row>
     <row r="14">
@@ -2225,36 +1872,28 @@
       <c r="E14" s="5" t="n">
         <v>7475</v>
       </c>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Changes in operating assets and liabilities: &gt; Cash generated by operating activities / Investing activities: &gt; Cash generated by operating activities</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="7" t="n">
         <v>118254</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="7" t="n">
         <v>110543</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="7" t="n">
         <v>122151</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="7" t="n">
         <v>104038</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="7" t="n">
         <v>80674</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>69391</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <v>77434</v>
       </c>
     </row>
     <row r="16">
@@ -2263,9 +1902,9 @@
           <t>Changes in operating assets and liabilities: &gt; Deferred revenue</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="6" t="n">
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="5" t="n">
         <v>478</v>
       </c>
       <c r="E16" s="5" t="n">
@@ -2274,12 +1913,6 @@
       <c r="F16" s="5" t="n">
         <v>2081</v>
       </c>
-      <c r="G16" s="6" t="n">
-        <v>-625</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>-3</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2287,22 +1920,16 @@
           <t>Investing activities: &gt; Other current and non-current liabilities</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="5" t="n">
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="6" t="n">
         <v>5632</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="6" t="n">
         <v>5799</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="6" t="n">
         <v>8916</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>-4700</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>38449</v>
       </c>
     </row>
     <row r="18">
@@ -2311,8 +1938,8 @@
           <t>Investing activities: &gt; Purchases of marketable securities</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
       <c r="D18" s="5" t="n">
         <v>-76923</v>
       </c>
@@ -2322,12 +1949,6 @@
       <c r="F18" s="5" t="n">
         <v>-114938</v>
       </c>
-      <c r="G18" s="5" t="n">
-        <v>-39630</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>-71356</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2335,22 +1956,16 @@
           <t>Investing activities: &gt; Proceeds from maturities of marketable securities</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="5" t="n">
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="6" t="n">
         <v>29917</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="6" t="n">
         <v>59023</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="6" t="n">
         <v>69918</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>40102</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>55881</v>
       </c>
     </row>
     <row r="20">
@@ -2359,8 +1974,8 @@
           <t>Investing activities: &gt; Proceeds from sales of marketable securities</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
       <c r="D20" s="5" t="n">
         <v>37446</v>
       </c>
@@ -2370,12 +1985,6 @@
       <c r="F20" s="5" t="n">
         <v>50473</v>
       </c>
-      <c r="G20" s="5" t="n">
-        <v>56988</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>47838</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2383,22 +1992,16 @@
           <t>Investing activities: &gt; Payments for acquisition of property, plant and equipment</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="5" t="n">
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="6" t="n">
         <v>-10708</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="6" t="n">
         <v>-11085</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="6" t="n">
         <v>-7309</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>-10495</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>-13313</v>
       </c>
     </row>
     <row r="22">
@@ -2416,39 +2019,31 @@
       <c r="D22" s="5" t="n">
         <v>-2086</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="5" t="n">
         <v>-385</v>
       </c>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Investing activities: &gt; Cash generated by/(used in) investing activities / Financing activities: &gt; Cash used in investing activities / Financing activities: &gt; Cash generated by/(used in) investing activities</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Investing activities: &gt; Cash generated by/(used in) investing activities / Financing activities: &gt; Cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
         <v>2935</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="7" t="n">
         <v>-22354</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="7" t="n">
         <v>-14545</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="7" t="n">
         <v>-4289</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>45896</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>16066</v>
       </c>
     </row>
     <row r="24">
@@ -2457,23 +2052,17 @@
           <t>Financing activities: &gt; Payments made in connection with business acquisitions, net</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="6" t="n">
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="5" t="n">
         <v>-306</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="5" t="n">
         <v>-33</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>-1524</v>
       </c>
-      <c r="G24" s="6" t="n">
-        <v>-624</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>-721</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2481,20 +2070,16 @@
           <t>Financing activities: &gt; Payments for taxes related to net share settlement of equity awards</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="5" t="n">
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="6" t="n">
+        <v>-6223</v>
+      </c>
+      <c r="E25" s="6" t="n">
         <v>-6556</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="6" t="n">
         <v>-3634</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>-2817</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>-2527</v>
       </c>
     </row>
     <row r="26">
@@ -2503,380 +2088,208 @@
           <t>Financing activities: &gt; Other</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="6" t="n">
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="5" t="n">
         <v>-160</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="5" t="n">
         <v>976</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="5" t="n">
         <v>754</v>
       </c>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Financing activities: &gt; Purchases of non-marketable securities</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
+          <t>Financing activities: &gt; Payments for dividends and dividend equivalents</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="6" t="n">
+        <v>-14841</v>
+      </c>
       <c r="E27" s="6" t="n">
-        <v>-131</v>
+        <v>-14467</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-210</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>-1001</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>-1871</v>
+        <v>-14081</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Financing activities: &gt; Payments for dividends and dividend equivalents</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
+          <t>Financing activities: &gt; Repurchases of common stock</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="5" t="n">
+        <v>-89402</v>
+      </c>
       <c r="E28" s="5" t="n">
-        <v>-14467</v>
+        <v>-85971</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-14081</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>-14119</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>-13712</v>
+        <v>-72358</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Financing activities: &gt; Proceeds from non-marketable securities</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
+          <t>Financing activities: &gt; Proceeds from issuance of term debt, net</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="6" t="n">
+        <v>5465</v>
+      </c>
       <c r="E29" s="6" t="n">
-        <v>387</v>
+        <v>20393</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>92</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>1634</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>353</v>
+        <v>16091</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Financing activities: &gt; Repurchases of common stock</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
+          <t>Financing activities: &gt; Repayments of term debt</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="5" t="n">
+        <v>-9543</v>
+      </c>
       <c r="E30" s="5" t="n">
-        <v>-85971</v>
+        <v>-8750</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-72358</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>-66897</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>-72738</v>
+        <v>-12629</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Financing activities: &gt; Proceeds from issuance of term debt, net</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="5" t="n">
-        <v>20393</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>16091</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>6963</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>6969</v>
+          <t>Financing activities: &gt; Proceeds from/(Repayments of) commercial paper, net</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="6" t="n">
+        <v>3955</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>1022</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-963</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Financing activities: &gt; Repayments of term debt / Supplemental cash flow disclosure: &gt; Repayments of term debt</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr"/>
-      <c r="C32" s="11" t="inlineStr"/>
-      <c r="D32" s="9" t="n">
-        <v>-9543</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>-8750</v>
-      </c>
-      <c r="F32" s="9" t="n">
-        <v>-12629</v>
-      </c>
-      <c r="G32" s="9" t="n">
-        <v>-8805</v>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>-6500</v>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Financing activities: &gt; Cash used in financing activities / Supplemental cash flow disclosure: &gt; Cash used in financing activities</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>-121983</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>-108488</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>-110749</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>-93353</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>-86820</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Financing activities: &gt; Proceeds from/(Repayments of) commercial paper, net / Supplemental cash flow disclosure: &gt; Proceeds from/(Repayments of) commercial paper, net / Supplemental cash flow disclosure: &gt; Repayments of commercial paper, net</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr"/>
-      <c r="C33" s="11" t="inlineStr"/>
-      <c r="D33" s="9" t="n">
-        <v>3955</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>1022</v>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>-963</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>-5977</v>
-      </c>
-      <c r="H33" s="13" t="n">
-        <v>-37</v>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Financing activities: &gt; Increase/(Decrease) in cash, cash equivalents, and restricted cash and cash equivalents / Financing activities: &gt; Increase/(Decrease) in cash, cash equivalents and restricted cash / Supplemental cash flow disclosure: &gt; Decrease in cash, cash equivalents and restricted cash</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>-794</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>5760</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>-10952</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>-3860</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>-10435</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Financing activities: &gt; Proceeds from issuance of common stock</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="5" t="n">
-        <v>1105</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>880</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>781</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>669</v>
+          <t>Financing activities: &gt; Cash, cash equivalents, and restricted cash and cash equivalents, ending balances / Financing activities: &gt; Cash, cash equivalents and restricted cash, ending balances / Supplemental cash flow disclosure: &gt; Cash, cash equivalents and restricted cash, ending balances</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>29943</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>30737</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>24977</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>35929</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>39789</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Financing activities: &gt; Cash used in financing activities / Supplemental cash flow disclosure: &gt; Cash used in financing activities</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="n">
-        <v>-121983</v>
-      </c>
-      <c r="C35" s="9" t="n">
-        <v>-108488</v>
-      </c>
-      <c r="D35" s="9" t="n">
-        <v>-110749</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>-93353</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <v>-86820</v>
-      </c>
-      <c r="G35" s="9" t="n">
-        <v>-90976</v>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>-87876</v>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Supplemental cash flow disclosure: &gt; Cash paid for income taxes, net</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="6" t="n">
+        <v>19573</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>25385</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>9501</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Financing activities: &gt; Increase/(Decrease) in cash, cash equivalents, and restricted cash and cash equivalents / Financing activities: &gt; Increase/(Decrease) in cash, cash equivalents and restricted cash / Supplemental cash flow disclosure: &gt; Decrease in cash, cash equivalents and restricted cash</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="n">
-        <v>-794</v>
-      </c>
-      <c r="C36" s="9" t="n">
-        <v>5760</v>
-      </c>
-      <c r="D36" s="9" t="n">
-        <v>-10952</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>-3860</v>
-      </c>
-      <c r="F36" s="9" t="n">
-        <v>-10435</v>
-      </c>
-      <c r="G36" s="11" t="inlineStr"/>
-      <c r="H36" s="11" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Financing activities: &gt; Cash, cash equivalents, and restricted cash and cash equivalents, ending balances / Financing activities: &gt; Cash, cash equivalents and restricted cash, ending balances</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="n">
-        <v>29943</v>
-      </c>
-      <c r="C37" s="9" t="n">
-        <v>30737</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>24977</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>35929</v>
-      </c>
-      <c r="F37" s="11" t="inlineStr"/>
-      <c r="G37" s="11" t="inlineStr"/>
-      <c r="H37" s="11" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Supplemental cash flow disclosure: &gt; Cash paid for income taxes, net</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="5" t="n">
-        <v>25385</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>9501</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>15263</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>10417</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Supplemental cash flow disclosure: &gt; Cash paid for interest</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="5" t="n">
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="5" t="n">
+        <v>2865</v>
+      </c>
+      <c r="E36" s="5" t="n">
         <v>2687</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F36" s="5" t="n">
         <v>3002</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>3423</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>3022</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Supplemental cash flow disclosure: &gt; Cash, cash equivalents and restricted cash, ending balances</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="12" t="n"/>
-      <c r="E40" s="5" t="n">
-        <v>35929</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>39789</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>50224</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>25913</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>Supplemental cash flow disclosure: &gt; Other</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="12" t="n"/>
-      <c r="E41" s="6" t="n">
-        <v>-129</v>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>-126</v>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>-105</v>
-      </c>
-      <c r="H41" s="12" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>Supplemental cash flow disclosure: &gt; Increase/(Decrease) in cash, cash equivalents and restricted cash</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12" t="n"/>
-      <c r="E42" s="5" t="n">
-        <v>-3860</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>-10435</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>24311</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>5624</v>
       </c>
     </row>
   </sheetData>
